--- a/filer/19982912_rynkeby.xlsx
+++ b/filer/19982912_rynkeby.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/19982912_rynkeby.xlsx
+++ b/filer/19982912_rynkeby.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_19982912" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_19982912" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_19982912" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_19982912" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -190,11 +191,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -595,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -629,7 +630,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -644,35 +645,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1498,35 +1499,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2832,35 +2833,35 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
@@ -3296,49 +3297,49 @@
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B61" s="11">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B61" s="8">
         <f>'balance_raw_19982912'!$B$38</f>
         <v/>
       </c>
-      <c r="C61" s="11">
+      <c r="C61" s="8">
         <f>'balance_raw_19982912'!$C$38</f>
         <v/>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="8">
         <f>'balance_raw_19982912'!$D$38</f>
         <v/>
       </c>
-      <c r="E61" s="11">
+      <c r="E61" s="8">
         <f>'balance_raw_19982912'!$E$38</f>
         <v/>
       </c>
-      <c r="F61" s="11">
+      <c r="F61" s="8">
         <f>'balance_raw_19982912'!$F$38</f>
         <v/>
       </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" s="12">
+      <c r="H61" s="9">
         <f>IFERROR(B61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="I61" s="12">
+      <c r="I61" s="9">
         <f>IFERROR(C61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="J61" s="12">
+      <c r="J61" s="9">
         <f>IFERROR(D61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="K61" s="12">
+      <c r="K61" s="9">
         <f>IFERROR(E61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="L61" s="12">
+      <c r="L61" s="9">
         <f>IFERROR(F61/$B$61*100,"")</f>
         <v/>
       </c>
@@ -3346,7 +3347,7 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B62" s="5">
@@ -3394,7 +3395,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Kreditinstitutter</t>
         </is>
       </c>
       <c r="B63" s="8">
@@ -3442,7 +3443,7 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Kreditinstitutter</t>
+          <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
       <c r="B64" s="5">
@@ -3490,7 +3491,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
       <c r="B65" s="8">
@@ -3538,7 +3539,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B66" s="5">
@@ -3586,7 +3587,7 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B67" s="8">
@@ -3634,7 +3635,7 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B68" s="5">
@@ -3682,7 +3683,7 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
       <c r="B69" s="8">
@@ -3730,7 +3731,7 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+          <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
       <c r="B70" s="5">
@@ -3778,7 +3779,7 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
+          <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
       <c r="B71" s="8">
@@ -3824,49 +3825,49 @@
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B72" s="5">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B72" s="11">
         <f>'balance_raw_19982912'!$B$49</f>
         <v/>
       </c>
-      <c r="C72" s="5">
+      <c r="C72" s="11">
         <f>'balance_raw_19982912'!$C$49</f>
         <v/>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="11">
         <f>'balance_raw_19982912'!$D$49</f>
         <v/>
       </c>
-      <c r="E72" s="5">
+      <c r="E72" s="11">
         <f>'balance_raw_19982912'!$E$49</f>
         <v/>
       </c>
-      <c r="F72" s="5">
+      <c r="F72" s="11">
         <f>'balance_raw_19982912'!$F$49</f>
         <v/>
       </c>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" s="6">
+      <c r="H72" s="12">
         <f>IFERROR(B72/$B$72*100,"")</f>
         <v/>
       </c>
-      <c r="I72" s="6">
+      <c r="I72" s="12">
         <f>IFERROR(C72/$B$72*100,"")</f>
         <v/>
       </c>
-      <c r="J72" s="6">
+      <c r="J72" s="12">
         <f>IFERROR(D72/$B$72*100,"")</f>
         <v/>
       </c>
-      <c r="K72" s="6">
+      <c r="K72" s="12">
         <f>IFERROR(E72/$B$72*100,"")</f>
         <v/>
       </c>
-      <c r="L72" s="6">
+      <c r="L72" s="12">
         <f>IFERROR(F72/$B$72*100,"")</f>
         <v/>
       </c>
@@ -3874,7 +3875,7 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>Kortfristede gældsforpligtelser</t>
+          <t>Gældsforpligtelser</t>
         </is>
       </c>
       <c r="B73" s="11">
@@ -3922,7 +3923,7 @@
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>Gældsforpligtelser</t>
+          <t>Passiver</t>
         </is>
       </c>
       <c r="B74" s="11">
@@ -3967,100 +3968,100 @@
         <v/>
       </c>
     </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B75" s="11">
-        <f>'balance_raw_19982912'!$B$52</f>
-        <v/>
-      </c>
-      <c r="C75" s="11">
-        <f>'balance_raw_19982912'!$C$52</f>
-        <v/>
-      </c>
-      <c r="D75" s="11">
-        <f>'balance_raw_19982912'!$D$52</f>
-        <v/>
-      </c>
-      <c r="E75" s="11">
-        <f>'balance_raw_19982912'!$E$52</f>
-        <v/>
-      </c>
-      <c r="F75" s="11">
-        <f>'balance_raw_19982912'!$F$52</f>
-        <v/>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" s="12">
-        <f>IFERROR(B75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="I75" s="12">
-        <f>IFERROR(C75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="J75" s="12">
-        <f>IFERROR(D75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="K75" s="12">
-        <f>IFERROR(E75/$B$75*100,"")</f>
-        <v/>
-      </c>
-      <c r="L75" s="12">
-        <f>IFERROR(F75/$B$75*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>NØGLEOPLYSNINGER</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C77" s="3" t="n">
+      <c r="B76" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="C76" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="D76" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F77" s="3" t="n">
+      <c r="E76" s="3" t="n">
         <v>2024</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Gns. antal medarbejdere</t>
+        </is>
+      </c>
+      <c r="B77" s="8">
+        <f>'res_raw_19982912'!$B$19</f>
+        <v/>
+      </c>
+      <c r="C77" s="8">
+        <f>'res_raw_19982912'!$C$19</f>
+        <v/>
+      </c>
+      <c r="D77" s="8">
+        <f>'res_raw_19982912'!$D$19</f>
+        <v/>
+      </c>
+      <c r="E77" s="8">
+        <f>'res_raw_19982912'!$E$19</f>
+        <v/>
+      </c>
+      <c r="F77" s="8">
+        <f>'res_raw_19982912'!$F$19</f>
+        <v/>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" s="9">
+        <f>IFERROR(B77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="I77" s="9">
+        <f>IFERROR(C77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="J77" s="9">
+        <f>IFERROR(D77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="K77" s="9">
+        <f>IFERROR(E77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="L77" s="9">
+        <f>IFERROR(F77/$B$77*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Gns. antal medarbejdere</t>
+          <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
       <c r="B78" s="5">
-        <f>'res_raw_19982912'!$B$19</f>
+        <f>'res_raw_19982912'!$B$20</f>
         <v/>
       </c>
       <c r="C78" s="5">
-        <f>'res_raw_19982912'!$C$19</f>
+        <f>'res_raw_19982912'!$C$20</f>
         <v/>
       </c>
       <c r="D78" s="5">
-        <f>'res_raw_19982912'!$D$19</f>
+        <f>'res_raw_19982912'!$D$20</f>
         <v/>
       </c>
       <c r="E78" s="5">
-        <f>'res_raw_19982912'!$E$19</f>
+        <f>'res_raw_19982912'!$E$20</f>
         <v/>
       </c>
       <c r="F78" s="5">
-        <f>'res_raw_19982912'!$F$19</f>
+        <f>'res_raw_19982912'!$F$20</f>
         <v/>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -4085,370 +4086,464 @@
         <v/>
       </c>
     </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>Investering i materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B79" s="8">
-        <f>'res_raw_19982912'!$B$20</f>
-        <v/>
-      </c>
-      <c r="C79" s="8">
-        <f>'res_raw_19982912'!$C$20</f>
-        <v/>
-      </c>
-      <c r="D79" s="8">
-        <f>'res_raw_19982912'!$D$20</f>
-        <v/>
-      </c>
-      <c r="E79" s="8">
-        <f>'res_raw_19982912'!$E$20</f>
-        <v/>
-      </c>
-      <c r="F79" s="8">
-        <f>'res_raw_19982912'!$F$20</f>
-        <v/>
-      </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" s="9">
-        <f>IFERROR(B79/$B$79*100,"")</f>
-        <v/>
-      </c>
-      <c r="I79" s="9">
-        <f>IFERROR(C79/$B$79*100,"")</f>
-        <v/>
-      </c>
-      <c r="J79" s="9">
-        <f>IFERROR(D79/$B$79*100,"")</f>
-        <v/>
-      </c>
-      <c r="K79" s="9">
-        <f>IFERROR(E79/$B$79*100,"")</f>
-        <v/>
-      </c>
-      <c r="L79" s="9">
-        <f>IFERROR(F79/$B$79*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="3" t="inlineStr">
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>NØGLETAL</t>
         </is>
       </c>
-      <c r="B81" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C81" s="3" t="n">
+      <c r="B80" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="C80" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="D80" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F81" s="3" t="n">
+      <c r="E80" s="3" t="n">
         <v>2024</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Afkastningsgrad, %</t>
+        </is>
+      </c>
+      <c r="B81" s="13">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="C81" s="13">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="D81" s="13">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="E81" s="13">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="F81" s="13">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$49*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Afkastningsgrad, %</t>
-        </is>
-      </c>
-      <c r="B82" s="13">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="C82" s="13">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="D82" s="13">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="E82" s="13">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="F82" s="13">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$49*100,"")</f>
+          <t>Overskudsgrad, %</t>
+        </is>
+      </c>
+      <c r="B82" s="14">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="C82" s="14">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="D82" s="14">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="E82" s="14">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="F82" s="14">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Overskudsgrad, %</t>
-        </is>
-      </c>
-      <c r="B83" s="14">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="C83" s="14">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="D83" s="14">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="E83" s="14">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="F83" s="14">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
+          <t>Aktivernes omsætningshastighed, gange</t>
+        </is>
+      </c>
+      <c r="B83" s="13">
+        <f>IFERROR($B$4/$B$49,"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="13">
+        <f>IFERROR($C$4/$C$49,"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="13">
+        <f>IFERROR($D$4/$D$49,"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="13">
+        <f>IFERROR($E$4/$E$49,"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="13">
+        <f>IFERROR($F$4/$F$49,"")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
-        </is>
-      </c>
-      <c r="B84" s="13">
-        <f>IFERROR($B$4/$B$49,"")</f>
-        <v/>
-      </c>
-      <c r="C84" s="13">
-        <f>IFERROR($C$4/$C$49,"")</f>
-        <v/>
-      </c>
-      <c r="D84" s="13">
-        <f>IFERROR($D$4/$D$49,"")</f>
-        <v/>
-      </c>
-      <c r="E84" s="13">
-        <f>IFERROR($E$4/$E$49,"")</f>
-        <v/>
-      </c>
-      <c r="F84" s="13">
-        <f>IFERROR($F$4/$F$49,"")</f>
+          <t>Egenkapitalens forrentning, %</t>
+        </is>
+      </c>
+      <c r="B84" s="14">
+        <f>IFERROR($B$18/$B$58*100,"")</f>
+        <v/>
+      </c>
+      <c r="C84" s="14">
+        <f>IFERROR($C$18/$C$58*100,"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="14">
+        <f>IFERROR($D$18/$D$58*100,"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="14">
+        <f>IFERROR($E$18/$E$58*100,"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="14">
+        <f>IFERROR($F$18/$F$58*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Egenkapitalens forrentning, %</t>
-        </is>
-      </c>
-      <c r="B85" s="14">
-        <f>IFERROR($B$18/$B$58*100,"")</f>
-        <v/>
-      </c>
-      <c r="C85" s="14">
-        <f>IFERROR($C$18/$C$58*100,"")</f>
-        <v/>
-      </c>
-      <c r="D85" s="14">
-        <f>IFERROR($D$18/$D$58*100,"")</f>
-        <v/>
-      </c>
-      <c r="E85" s="14">
-        <f>IFERROR($E$18/$E$58*100,"")</f>
-        <v/>
-      </c>
-      <c r="F85" s="14">
-        <f>IFERROR($F$18/$F$58*100,"")</f>
+          <t>Gældsrente, %</t>
+        </is>
+      </c>
+      <c r="B85" s="13">
+        <f>IFERROR($B$16/($B$74-$B$58)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="13">
+        <f>IFERROR($C$16/($C$74-$C$58)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D85" s="13">
+        <f>IFERROR($D$16/($D$74-$D$58)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="13">
+        <f>IFERROR($E$16/($E$74-$E$58)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="13">
+        <f>IFERROR($F$16/($F$74-$F$58)*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Gældsrente, %</t>
-        </is>
-      </c>
-      <c r="B86" s="13">
-        <f>IFERROR($B$16/($B$75-$B$58)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C86" s="13">
-        <f>IFERROR($C$16/($C$75-$C$58)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D86" s="13">
-        <f>IFERROR($D$16/($D$75-$D$58)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E86" s="13">
-        <f>IFERROR($E$16/($E$75-$E$58)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F86" s="13">
-        <f>IFERROR($F$16/($F$75-$F$58)*100,"")</f>
+          <t>Soliditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B86" s="14">
+        <f>IFERROR($B$58/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="14">
+        <f>IFERROR($C$58/$C$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="D86" s="14">
+        <f>IFERROR($D$58/$D$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="E86" s="14">
+        <f>IFERROR($E$58/$E$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="F86" s="14">
+        <f>IFERROR($F$58/$F$49*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Soliditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B87" s="14">
-        <f>IFERROR($B$58/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="C87" s="14">
-        <f>IFERROR($C$58/$C$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="D87" s="14">
-        <f>IFERROR($D$58/$D$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="E87" s="14">
-        <f>IFERROR($E$58/$E$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="F87" s="14">
-        <f>IFERROR($F$58/$F$49*100,"")</f>
+          <t>Gearing</t>
+        </is>
+      </c>
+      <c r="B87" s="13">
+        <f>IFERROR(($B$74-$B$58)/$B$58,"")</f>
+        <v/>
+      </c>
+      <c r="C87" s="13">
+        <f>IFERROR(($C$74-$C$58)/$C$58,"")</f>
+        <v/>
+      </c>
+      <c r="D87" s="13">
+        <f>IFERROR(($D$74-$D$58)/$D$58,"")</f>
+        <v/>
+      </c>
+      <c r="E87" s="13">
+        <f>IFERROR(($E$74-$E$58)/$E$58,"")</f>
+        <v/>
+      </c>
+      <c r="F87" s="13">
+        <f>IFERROR(($F$74-$F$58)/$F$58,"")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Gearing</t>
-        </is>
-      </c>
-      <c r="B88" s="13">
-        <f>IFERROR(($B$75-$B$58)/$B$58,"")</f>
-        <v/>
-      </c>
-      <c r="C88" s="13">
-        <f>IFERROR(($C$75-$C$58)/$C$58,"")</f>
-        <v/>
-      </c>
-      <c r="D88" s="13">
-        <f>IFERROR(($D$75-$D$58)/$D$58,"")</f>
-        <v/>
-      </c>
-      <c r="E88" s="13">
-        <f>IFERROR(($E$75-$E$58)/$E$58,"")</f>
-        <v/>
-      </c>
-      <c r="F88" s="13">
-        <f>IFERROR(($F$75-$F$58)/$F$58,"")</f>
+          <t>Likviditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B88" s="14">
+        <f>IFERROR($B$48/$B$72*100,"")</f>
+        <v/>
+      </c>
+      <c r="C88" s="14">
+        <f>IFERROR($C$48/$C$72*100,"")</f>
+        <v/>
+      </c>
+      <c r="D88" s="14">
+        <f>IFERROR($D$48/$D$72*100,"")</f>
+        <v/>
+      </c>
+      <c r="E88" s="14">
+        <f>IFERROR($E$48/$E$72*100,"")</f>
+        <v/>
+      </c>
+      <c r="F88" s="14">
+        <f>IFERROR($F$48/$F$72*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Likviditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B89" s="14">
-        <f>IFERROR($B$48/$B$73*100,"")</f>
-        <v/>
-      </c>
-      <c r="C89" s="14">
-        <f>IFERROR($C$48/$C$73*100,"")</f>
-        <v/>
-      </c>
-      <c r="D89" s="14">
-        <f>IFERROR($D$48/$D$73*100,"")</f>
-        <v/>
-      </c>
-      <c r="E89" s="14">
-        <f>IFERROR($E$48/$E$73*100,"")</f>
-        <v/>
-      </c>
-      <c r="F89" s="14">
-        <f>IFERROR($F$48/$F$73*100,"")</f>
+          <t>Rentemarginal, %</t>
+        </is>
+      </c>
+      <c r="B89" s="13">
+        <f>IFERROR(B81-B85,"")</f>
+        <v/>
+      </c>
+      <c r="C89" s="13">
+        <f>IFERROR(C81-C85,"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="13">
+        <f>IFERROR(D81-D85,"")</f>
+        <v/>
+      </c>
+      <c r="E89" s="13">
+        <f>IFERROR(E81-E85,"")</f>
+        <v/>
+      </c>
+      <c r="F89" s="13">
+        <f>IFERROR(F81-F85,"")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Rentemarginal, %</t>
-        </is>
-      </c>
-      <c r="B90" s="13">
-        <f>IFERROR(B82-B86,"")</f>
-        <v/>
-      </c>
-      <c r="C90" s="13">
-        <f>IFERROR(C82-C86,"")</f>
-        <v/>
-      </c>
-      <c r="D90" s="13">
-        <f>IFERROR(D82-D86,"")</f>
-        <v/>
-      </c>
-      <c r="E90" s="13">
-        <f>IFERROR(E82-E86,"")</f>
-        <v/>
-      </c>
-      <c r="F90" s="13">
-        <f>IFERROR(F82-F86,"")</f>
+          <t>Gældsandel, %</t>
+        </is>
+      </c>
+      <c r="B90" s="14">
+        <f>IFERROR(($B$74-$B$58)/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="C90" s="14">
+        <f>IFERROR(($C$74-$C$58)/$C$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="D90" s="14">
+        <f>IFERROR(($D$74-$D$58)/$D$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="E90" s="14">
+        <f>IFERROR(($E$74-$E$58)/$E$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="F90" s="14">
+        <f>IFERROR(($F$74-$F$58)/$F$49*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Gældsandel, %</t>
-        </is>
-      </c>
-      <c r="B91" s="14">
-        <f>IFERROR(($B$75-$B$58)/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="C91" s="14">
-        <f>IFERROR(($C$75-$C$58)/$C$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="D91" s="14">
-        <f>IFERROR(($D$75-$D$58)/$D$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="E91" s="14">
-        <f>IFERROR(($E$75-$E$58)/$E$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="F91" s="14">
-        <f>IFERROR(($F$75-$F$58)/$F$49*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
           <t>Kapitalbindingsgrad, %</t>
         </is>
       </c>
-      <c r="B92" s="13">
-        <f>IFERROR($B$33/($B$58+$B$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C92" s="13">
-        <f>IFERROR($C$33/($C$58+$C$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D92" s="13">
-        <f>IFERROR($D$33/($D$58+$D$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E92" s="13">
-        <f>IFERROR($E$33/($E$58+$E$61)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F92" s="13">
-        <f>IFERROR($F$33/($F$58+$F$61)*100,"")</f>
+      <c r="B91" s="13">
+        <f>IFERROR($B$33/($B$58+0)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C91" s="13">
+        <f>IFERROR($C$33/($C$58+0)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D91" s="13">
+        <f>IFERROR($D$33/($D$58+0)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E91" s="13">
+        <f>IFERROR($E$33/($E$58+0)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F91" s="13">
+        <f>IFERROR($F$33/($F$58+0)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B94" s="17">
+        <f>'pengestrom_raw_19982912'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C94" s="17">
+        <f>'pengestrom_raw_19982912'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D94" s="17">
+        <f>'pengestrom_raw_19982912'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E94" s="17">
+        <f>'pengestrom_raw_19982912'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F94" s="17">
+        <f>'pengestrom_raw_19982912'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B95" s="17">
+        <f>'pengestrom_raw_19982912'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C95" s="17">
+        <f>'pengestrom_raw_19982912'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D95" s="17">
+        <f>'pengestrom_raw_19982912'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E95" s="17">
+        <f>'pengestrom_raw_19982912'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F95" s="17">
+        <f>'pengestrom_raw_19982912'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B96" s="17">
+        <f>'pengestrom_raw_19982912'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C96" s="17">
+        <f>'pengestrom_raw_19982912'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D96" s="17">
+        <f>'pengestrom_raw_19982912'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E96" s="17">
+        <f>'pengestrom_raw_19982912'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F96" s="17">
+        <f>'pengestrom_raw_19982912'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B97" s="17">
+        <f>'pengestrom_raw_19982912'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C97" s="17">
+        <f>'pengestrom_raw_19982912'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D97" s="17">
+        <f>'pengestrom_raw_19982912'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E97" s="17">
+        <f>'pengestrom_raw_19982912'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F97" s="17">
+        <f>'pengestrom_raw_19982912'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B98">
+        <f>IF(ABS(('pengestrom_raw_19982912'!$B$2+'pengestrom_raw_19982912'!$B$3+'pengestrom_raw_19982912'!$B$4)-'pengestrom_raw_19982912'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_19982912'!$B$2+'pengestrom_raw_19982912'!$B$3+'pengestrom_raw_19982912'!$B$4)-'pengestrom_raw_19982912'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C98">
+        <f>IF(ABS(('pengestrom_raw_19982912'!$C$2+'pengestrom_raw_19982912'!$C$3+'pengestrom_raw_19982912'!$C$4)-'pengestrom_raw_19982912'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_19982912'!$C$2+'pengestrom_raw_19982912'!$C$3+'pengestrom_raw_19982912'!$C$4)-'pengestrom_raw_19982912'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D98">
+        <f>IF(ABS(('pengestrom_raw_19982912'!$D$2+'pengestrom_raw_19982912'!$D$3+'pengestrom_raw_19982912'!$D$4)-'pengestrom_raw_19982912'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_19982912'!$D$2+'pengestrom_raw_19982912'!$D$3+'pengestrom_raw_19982912'!$D$4)-'pengestrom_raw_19982912'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E98">
+        <f>IF(ABS(('pengestrom_raw_19982912'!$E$2+'pengestrom_raw_19982912'!$E$3+'pengestrom_raw_19982912'!$E$4)-'pengestrom_raw_19982912'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_19982912'!$E$2+'pengestrom_raw_19982912'!$E$3+'pengestrom_raw_19982912'!$E$4)-'pengestrom_raw_19982912'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F98">
+        <f>IF(ABS(('pengestrom_raw_19982912'!$F$2+'pengestrom_raw_19982912'!$F$3+'pengestrom_raw_19982912'!$F$4)-'pengestrom_raw_19982912'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_19982912'!$F$2+'pengestrom_raw_19982912'!$F$3+'pengestrom_raw_19982912'!$F$4)-'pengestrom_raw_19982912'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4481,390 +4576,392 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>849443</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>913041</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>977892</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>1026053</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>1132379</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>1111896</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>34159</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>20017</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>26642</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>22140</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>19298</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>21980</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>493383</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>528325</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>589891</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>625263</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>719829</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>681325</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>173902</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>207219</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>229677</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>215016</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>231008</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>253505</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>216317</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>197514</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>184966</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>207914</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>200840</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>199046</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>145916</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>128902</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>138343</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>139853</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>139836</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>137052</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>54473</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>52299</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>56235</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>57544</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>48900</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>49142</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>15928</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>16313</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>-9612</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>10517</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>12104</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>12852</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>101</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>920</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>153</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>2074</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>2709</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>1072</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>1889</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>2668</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>3056</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>1370</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>11102</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>15344</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>-12127</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>9535</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>13443</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>13771</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>9984</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>6284</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>-5360</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>4785</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>4111</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>5728</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>1118</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>9060</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>-6767</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>4750</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>9332</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>8043</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>248</v>
       </c>
-      <c r="C19" s="16" t="n">
-        <v>248</v>
-      </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>239</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>232</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>223</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>211</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>20340</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>58751</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>26569</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>15626</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>30127</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>22424</v>
       </c>
     </row>
   </sheetData>
@@ -4878,7 +4975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -4896,977 +4993,971 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>1411</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>165427</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>161782</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>158137</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>154492</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>150846</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>147200</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>173992</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>165453</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>156915</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>148377</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>139938</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>131400</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>419333</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>403726</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>393303</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>374963</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>356826</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>344541</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>78636</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>73414</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>76347</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>70221</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>64737</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>58740</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>173531</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>150671</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>172242</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>147936</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>161309</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>153244</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>3781</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>2858</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>3998</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>2907</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>3317</v>
       </c>
+      <c r="F8" s="17" t="n">
+        <v>3241</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>21362</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>65352</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>22470</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>30416</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>21480</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>22596</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>277310</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>292295</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>275057</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>251480</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>250843</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>237821</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>696643</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>696021</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>668360</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>626443</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>607669</v>
       </c>
+      <c r="F12" s="17" t="n">
+        <v>582362</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>31884</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>34621</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>36955</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>37886</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>35230</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>35142</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>2300</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>3418</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>3818</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>1701</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>4592</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>5665</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>38755</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>38772</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>45398</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>35360</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>52015</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>56809</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>72939</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>76811</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>86171</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>74947</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>91837</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>97616</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>69399</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>74719</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>110176</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>122666</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>137493</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>127385</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>47648</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>37997</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>75757</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>32470</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>50450</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>45565</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>587</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>2933</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>1280</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>458</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>707</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>398</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>2320</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>2040</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>2411</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>4329</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>2297</v>
       </c>
+      <c r="F20" s="17" t="n">
+        <v>3306</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>3381</v>
-      </c>
-      <c r="C23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>1146</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>191</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>168</v>
       </c>
+      <c r="F23" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
-        <v>123335</v>
-      </c>
-      <c r="C24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>118835</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>189624</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>160114</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>191115</v>
       </c>
+      <c r="F24" s="17" t="n">
+        <v>176654</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
-        <v>58146</v>
-      </c>
-      <c r="C26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>22597</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>23604</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>51107</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>34133</v>
       </c>
+      <c r="F26" s="17" t="n">
+        <v>31100</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
-        <v>254420</v>
-      </c>
-      <c r="C27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>218243</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>299399</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>286168</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>317085</v>
       </c>
+      <c r="F27" s="17" t="n">
+        <v>305370</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
-        <v>951063</v>
-      </c>
-      <c r="C28" s="16" t="n">
+      <c r="B28" s="17" t="n">
         <v>914264</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="C28" s="17" t="n">
         <v>967759</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>912611</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>924754</v>
       </c>
+      <c r="F28" s="17" t="n">
+        <v>887732</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>30000</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>30000</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>30000</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>30000</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="17" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>1101</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
-        <v>665098</v>
-      </c>
-      <c r="C34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>674158</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>667391</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>672141</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="E34" s="17" t="n">
         <v>681473</v>
       </c>
+      <c r="F34" s="17" t="n">
+        <v>613815</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
-        <v>695098</v>
-      </c>
-      <c r="C35" s="16" t="n">
+      <c r="B35" s="17" t="n">
         <v>704158</v>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="C35" s="17" t="n">
         <v>697391</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="D35" s="17" t="n">
         <v>702141</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="E35" s="17" t="n">
         <v>711473</v>
       </c>
+      <c r="F35" s="17" t="n">
+        <v>719516</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
-        <v>27272</v>
-      </c>
-      <c r="C36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>20772</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>13797</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>18196</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>23918</v>
       </c>
+      <c r="F36" s="17" t="n">
+        <v>26824</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
-        <v>27272</v>
-      </c>
-      <c r="C37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>32990</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>25725</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>21176</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>24849</v>
       </c>
+      <c r="F37" s="17" t="n">
+        <v>26824</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n">
-        <v>12987</v>
-      </c>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>87802</v>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>78764</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>98072</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>103134</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n">
+        <v>57304</v>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>132970</v>
+      </c>
+      <c r="D43" s="17" t="n">
+        <v>79332</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>60387</v>
+      </c>
+      <c r="F43" s="17" t="n">
+        <v>4188</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n">
-        <v>87882</v>
-      </c>
-      <c r="C43" s="16" t="n">
-        <v>87802</v>
-      </c>
-      <c r="D43" s="16" t="n">
-        <v>78879</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>78764</v>
-      </c>
-      <c r="F43" s="16" t="n">
-        <v>98072</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n">
-        <v>87780</v>
-      </c>
-      <c r="C44" s="16" t="n">
-        <v>57304</v>
-      </c>
-      <c r="D44" s="16" t="n">
-        <v>132970</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>79332</v>
-      </c>
-      <c r="F44" s="16" t="n">
-        <v>60387</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
+      <c r="C45" s="17" t="n">
+        <v>6290</v>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>2585</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n">
-        <v>1759</v>
-      </c>
-      <c r="C46" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="16" t="n">
-        <v>6290</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="16" t="n"/>
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>32010</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>26504</v>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>31198</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>29973</v>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>31485</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>38285</v>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>32010</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>26504</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>31198</v>
-      </c>
-      <c r="F48" s="16" t="n">
-        <v>29973</v>
-      </c>
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>177116</v>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>244643</v>
+      </c>
+      <c r="D49" s="17" t="n">
+        <v>189294</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>188432</v>
+      </c>
+      <c r="F49" s="17" t="n">
+        <v>141392</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n">
-        <v>215706</v>
-      </c>
-      <c r="C50" s="16" t="n">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
         <v>177116</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>244643</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>189294</v>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>188432</v>
       </c>
+      <c r="F50" s="17" t="n">
+        <v>141392</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="inlineStr">
-        <is>
-          <t>Gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="n">
-        <v>228693</v>
-      </c>
-      <c r="C51" s="16" t="n">
-        <v>177116</v>
-      </c>
-      <c r="D51" s="16" t="n">
-        <v>244643</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>189294</v>
-      </c>
-      <c r="F51" s="16" t="n">
-        <v>188432</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
-        <v>951063</v>
-      </c>
-      <c r="C52" s="16" t="n">
+      <c r="B51" s="17" t="n">
         <v>914264</v>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="C51" s="17" t="n">
         <v>967759</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="D51" s="17" t="n">
         <v>912611</v>
       </c>
-      <c r="F52" s="16" t="n">
+      <c r="E51" s="17" t="n">
         <v>924754</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>887732</v>
       </c>
     </row>
   </sheetData>
@@ -5875,6 +5966,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>47654</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>-7670</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>60347</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>48477</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>77070</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-51675</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-28573</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-15626</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-30127</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-23835</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-30476</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>37906</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-10351</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-36925</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-56199</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5905,13 +6118,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6346,15 +6559,15 @@
         </is>
       </c>
       <c r="B24" s="24">
-        <f>'balance_raw_19982912'!$F$52-'balance_raw_19982912'!$F$35</f>
+        <f>'balance_raw_19982912'!$F$51-'balance_raw_19982912'!$F$35</f>
         <v/>
       </c>
       <c r="C24" s="24">
-        <f>'balance_raw_19982912'!$E$52-'balance_raw_19982912'!$E$35</f>
+        <f>'balance_raw_19982912'!$E$51-'balance_raw_19982912'!$E$35</f>
         <v/>
       </c>
       <c r="D24" s="24">
-        <f>'balance_raw_19982912'!$D$52-'balance_raw_19982912'!$D$35</f>
+        <f>'balance_raw_19982912'!$D$51-'balance_raw_19982912'!$D$35</f>
         <v/>
       </c>
       <c r="F24" s="25" t="inlineStr">
@@ -6460,15 +6673,15 @@
         </is>
       </c>
       <c r="B30" s="24">
-        <f>'balance_raw_19982912'!$F$50</f>
+        <f>'balance_raw_19982912'!$F$49</f>
         <v/>
       </c>
       <c r="C30" s="24">
-        <f>'balance_raw_19982912'!$E$50</f>
+        <f>'balance_raw_19982912'!$E$49</f>
         <v/>
       </c>
       <c r="D30" s="24">
-        <f>'balance_raw_19982912'!$D$50</f>
+        <f>'balance_raw_19982912'!$D$49</f>
         <v/>
       </c>
       <c r="F30" s="25" t="inlineStr">
@@ -6625,7 +6838,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -6743,7 +6956,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -6919,7 +7132,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -6976,15 +7189,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF('balance_raw_19982912'!$F$52="","—",IF(ABS(B25-'balance_raw_19982912'!$F$52)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_19982912'!$F$52,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_19982912'!$F$51="","—",IF(ABS(B25-'balance_raw_19982912'!$F$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_19982912'!$F$51,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF('balance_raw_19982912'!$E$52="","—",IF(ABS(C25-'balance_raw_19982912'!$E$52)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_19982912'!$E$52,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_19982912'!$E$51="","—",IF(ABS(C25-'balance_raw_19982912'!$E$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_19982912'!$E$51,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF('balance_raw_19982912'!$D$52="","—",IF(ABS(D25-'balance_raw_19982912'!$D$52)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_19982912'!$D$52,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_19982912'!$D$51="","—",IF(ABS(D25-'balance_raw_19982912'!$D$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_19982912'!$D$51,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
